--- a/data/results/hr_logger_2hz_analysis.xlsx
+++ b/data/results/hr_logger_2hz_analysis.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\my_projects\esp32_wifi\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\my_projects\Git\motion-aware-hr-monitor\data\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{632EF8A3-D1FD-47F2-852B-5407C79EAD51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74D2215A-ABC1-4096-8D41-BFFF199AC0BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,9 +36,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="49">
   <si>
-    <t>sample_id</t>
-  </si>
-  <si>
     <t>hr_fft</t>
   </si>
   <si>
@@ -177,10 +174,13 @@
     <t>Notes</t>
   </si>
   <si>
-    <t>This workbook was generated from the filtered 100-row CSV log.</t>
-  </si>
-  <si>
     <t>Computed error is final HR minus external reference HR; absolute error is used for MAE and max error.</t>
+  </si>
+  <si>
+    <t>seconds</t>
+  </si>
+  <si>
+    <t>This workbook was generated from the filtered 60-row CSV log.</t>
   </si>
 </sst>
 </file>
@@ -559,10 +559,14 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="DataTable_2Hz" displayName="DataTable_2Hz" ref="A1:Q61">
   <tableColumns count="17">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="sample_id"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="seconds"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="hr_fft"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="conf_fft"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="peak_hz"/>
@@ -757,60 +761,60 @@
   <sheetData>
     <row r="1" spans="1:17" ht="14.65" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
       <c r="I1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:17">
       <c r="A2" s="3">
-        <v>165</v>
+        <v>0</v>
       </c>
       <c r="B2" s="3">
         <v>78</v>
@@ -834,7 +838,7 @@
         <v>0.54</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J2" s="3">
         <v>0.27</v>
@@ -865,7 +869,7 @@
     </row>
     <row r="3" spans="1:17">
       <c r="A3" s="3">
-        <v>166</v>
+        <v>1</v>
       </c>
       <c r="B3" s="3">
         <v>79.3</v>
@@ -889,7 +893,7 @@
         <v>0.6</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J3" s="3">
         <v>0.24</v>
@@ -920,7 +924,7 @@
     </row>
     <row r="4" spans="1:17">
       <c r="A4" s="3">
-        <v>167</v>
+        <v>2</v>
       </c>
       <c r="B4" s="3">
         <v>80</v>
@@ -944,7 +948,7 @@
         <v>0.68</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J4" s="3">
         <v>0.28000000000000003</v>
@@ -975,7 +979,7 @@
     </row>
     <row r="5" spans="1:17">
       <c r="A5" s="3">
-        <v>168</v>
+        <v>3</v>
       </c>
       <c r="B5" s="3">
         <v>80.3</v>
@@ -999,7 +1003,7 @@
         <v>0.69</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J5" s="3">
         <v>0.33</v>
@@ -1030,7 +1034,7 @@
     </row>
     <row r="6" spans="1:17">
       <c r="A6" s="3">
-        <v>169</v>
+        <v>4</v>
       </c>
       <c r="B6" s="3">
         <v>80.3</v>
@@ -1054,7 +1058,7 @@
         <v>0.59</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J6" s="3">
         <v>0.22</v>
@@ -1085,7 +1089,7 @@
     </row>
     <row r="7" spans="1:17">
       <c r="A7" s="3">
-        <v>170</v>
+        <v>5</v>
       </c>
       <c r="B7" s="3">
         <v>80.7</v>
@@ -1109,7 +1113,7 @@
         <v>0.79</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J7" s="3">
         <v>0.27</v>
@@ -1140,7 +1144,7 @@
     </row>
     <row r="8" spans="1:17">
       <c r="A8" s="3">
-        <v>171</v>
+        <v>6</v>
       </c>
       <c r="B8" s="3">
         <v>81.8</v>
@@ -1164,7 +1168,7 @@
         <v>0.74</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J8" s="3">
         <v>0.17</v>
@@ -1195,7 +1199,7 @@
     </row>
     <row r="9" spans="1:17">
       <c r="A9" s="3">
-        <v>172</v>
+        <v>7</v>
       </c>
       <c r="B9" s="3">
         <v>83.5</v>
@@ -1219,7 +1223,7 @@
         <v>0.69</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J9" s="3">
         <v>0.27</v>
@@ -1250,7 +1254,7 @@
     </row>
     <row r="10" spans="1:17">
       <c r="A10" s="3">
-        <v>173</v>
+        <v>8</v>
       </c>
       <c r="B10" s="3">
         <v>85</v>
@@ -1274,7 +1278,7 @@
         <v>0.7</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J10" s="3">
         <v>0.27</v>
@@ -1305,7 +1309,7 @@
     </row>
     <row r="11" spans="1:17">
       <c r="A11" s="3">
-        <v>174</v>
+        <v>9</v>
       </c>
       <c r="B11" s="3">
         <v>86.3</v>
@@ -1329,7 +1333,7 @@
         <v>0.47</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J11" s="3">
         <v>0.33</v>
@@ -1360,7 +1364,7 @@
     </row>
     <row r="12" spans="1:17">
       <c r="A12" s="3">
-        <v>175</v>
+        <v>10</v>
       </c>
       <c r="B12" s="3">
         <v>86.4</v>
@@ -1384,7 +1388,7 @@
         <v>0.53</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J12" s="3">
         <v>0.3</v>
@@ -1415,7 +1419,7 @@
     </row>
     <row r="13" spans="1:17">
       <c r="A13" s="3">
-        <v>176</v>
+        <v>11</v>
       </c>
       <c r="B13" s="3">
         <v>85.5</v>
@@ -1439,7 +1443,7 @@
         <v>0.41</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J13" s="3">
         <v>0.13</v>
@@ -1470,7 +1474,7 @@
     </row>
     <row r="14" spans="1:17">
       <c r="A14" s="3">
-        <v>177</v>
+        <v>12</v>
       </c>
       <c r="B14" s="3">
         <v>83.9</v>
@@ -1494,7 +1498,7 @@
         <v>0.41</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J14" s="3">
         <v>0.18</v>
@@ -1525,7 +1529,7 @@
     </row>
     <row r="15" spans="1:17">
       <c r="A15" s="3">
-        <v>178</v>
+        <v>13</v>
       </c>
       <c r="B15" s="3">
         <v>83.3</v>
@@ -1549,7 +1553,7 @@
         <v>0.51</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J15" s="3">
         <v>0.28999999999999998</v>
@@ -1580,7 +1584,7 @@
     </row>
     <row r="16" spans="1:17">
       <c r="A16" s="3">
-        <v>179</v>
+        <v>14</v>
       </c>
       <c r="B16" s="3">
         <v>81.900000000000006</v>
@@ -1604,7 +1608,7 @@
         <v>0.43</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J16" s="3">
         <v>0.3</v>
@@ -1635,7 +1639,7 @@
     </row>
     <row r="17" spans="1:17">
       <c r="A17" s="3">
-        <v>180</v>
+        <v>15</v>
       </c>
       <c r="B17" s="3">
         <v>80.599999999999994</v>
@@ -1659,7 +1663,7 @@
         <v>0.44</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J17" s="3">
         <v>0.31</v>
@@ -1690,7 +1694,7 @@
     </row>
     <row r="18" spans="1:17">
       <c r="A18" s="3">
-        <v>181</v>
+        <v>16</v>
       </c>
       <c r="B18" s="3">
         <v>81.3</v>
@@ -1714,7 +1718,7 @@
         <v>0.49</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J18" s="3">
         <v>0.24</v>
@@ -1745,7 +1749,7 @@
     </row>
     <row r="19" spans="1:17">
       <c r="A19" s="3">
-        <v>182</v>
+        <v>17</v>
       </c>
       <c r="B19" s="3">
         <v>82.5</v>
@@ -1769,7 +1773,7 @@
         <v>0.52</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J19" s="3">
         <v>0.12</v>
@@ -1800,7 +1804,7 @@
     </row>
     <row r="20" spans="1:17">
       <c r="A20" s="3">
-        <v>183</v>
+        <v>18</v>
       </c>
       <c r="B20" s="3">
         <v>83.4</v>
@@ -1824,7 +1828,7 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J20" s="3">
         <v>0.23</v>
@@ -1855,7 +1859,7 @@
     </row>
     <row r="21" spans="1:17">
       <c r="A21" s="3">
-        <v>184</v>
+        <v>19</v>
       </c>
       <c r="B21" s="3">
         <v>83.4</v>
@@ -1879,7 +1883,7 @@
         <v>0.54</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J21" s="3">
         <v>0.24</v>
@@ -1910,7 +1914,7 @@
     </row>
     <row r="22" spans="1:17">
       <c r="A22" s="3">
-        <v>185</v>
+        <v>20</v>
       </c>
       <c r="B22" s="3">
         <v>82.2</v>
@@ -1934,7 +1938,7 @@
         <v>0.53</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J22" s="3">
         <v>0.25</v>
@@ -1965,7 +1969,7 @@
     </row>
     <row r="23" spans="1:17">
       <c r="A23" s="3">
-        <v>186</v>
+        <v>21</v>
       </c>
       <c r="B23" s="3">
         <v>81</v>
@@ -1989,7 +1993,7 @@
         <v>0.49</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J23" s="3">
         <v>0.25</v>
@@ -2020,7 +2024,7 @@
     </row>
     <row r="24" spans="1:17">
       <c r="A24" s="3">
-        <v>187</v>
+        <v>22</v>
       </c>
       <c r="B24" s="3">
         <v>80.5</v>
@@ -2044,7 +2048,7 @@
         <v>0.51</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J24" s="3">
         <v>0.21</v>
@@ -2075,7 +2079,7 @@
     </row>
     <row r="25" spans="1:17">
       <c r="A25" s="3">
-        <v>188</v>
+        <v>23</v>
       </c>
       <c r="B25" s="3">
         <v>80.2</v>
@@ -2099,7 +2103,7 @@
         <v>0.51</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J25" s="3">
         <v>0.2</v>
@@ -2130,7 +2134,7 @@
     </row>
     <row r="26" spans="1:17">
       <c r="A26" s="3">
-        <v>189</v>
+        <v>24</v>
       </c>
       <c r="B26" s="3">
         <v>80.900000000000006</v>
@@ -2154,7 +2158,7 @@
         <v>0.72</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J26" s="3">
         <v>0.31</v>
@@ -2185,7 +2189,7 @@
     </row>
     <row r="27" spans="1:17">
       <c r="A27" s="3">
-        <v>190</v>
+        <v>25</v>
       </c>
       <c r="B27" s="3">
         <v>82.8</v>
@@ -2209,7 +2213,7 @@
         <v>0.81</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J27" s="3">
         <v>0.26</v>
@@ -2240,7 +2244,7 @@
     </row>
     <row r="28" spans="1:17">
       <c r="A28" s="3">
-        <v>191</v>
+        <v>26</v>
       </c>
       <c r="B28" s="3">
         <v>84.9</v>
@@ -2264,7 +2268,7 @@
         <v>0.38</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J28" s="3">
         <v>0.2</v>
@@ -2295,7 +2299,7 @@
     </row>
     <row r="29" spans="1:17">
       <c r="A29" s="3">
-        <v>192</v>
+        <v>27</v>
       </c>
       <c r="B29" s="3">
         <v>87.4</v>
@@ -2319,7 +2323,7 @@
         <v>0.51</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J29" s="3">
         <v>0.31</v>
@@ -2350,7 +2354,7 @@
     </row>
     <row r="30" spans="1:17">
       <c r="A30" s="3">
-        <v>193</v>
+        <v>28</v>
       </c>
       <c r="B30" s="3">
         <v>89.6</v>
@@ -2374,7 +2378,7 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J30" s="3">
         <v>0.35</v>
@@ -2405,7 +2409,7 @@
     </row>
     <row r="31" spans="1:17">
       <c r="A31" s="3">
-        <v>194</v>
+        <v>29</v>
       </c>
       <c r="B31" s="3">
         <v>90.1</v>
@@ -2429,7 +2433,7 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J31" s="3">
         <v>0.26</v>
@@ -2460,7 +2464,7 @@
     </row>
     <row r="32" spans="1:17">
       <c r="A32" s="3">
-        <v>195</v>
+        <v>30</v>
       </c>
       <c r="B32" s="3">
         <v>90</v>
@@ -2484,7 +2488,7 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J32" s="3">
         <v>0.28000000000000003</v>
@@ -2515,7 +2519,7 @@
     </row>
     <row r="33" spans="1:17">
       <c r="A33" s="3">
-        <v>196</v>
+        <v>31</v>
       </c>
       <c r="B33" s="3">
         <v>90.1</v>
@@ -2539,7 +2543,7 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J33" s="3">
         <v>0.16</v>
@@ -2570,7 +2574,7 @@
     </row>
     <row r="34" spans="1:17">
       <c r="A34" s="3">
-        <v>197</v>
+        <v>32</v>
       </c>
       <c r="B34" s="3">
         <v>90.2</v>
@@ -2594,7 +2598,7 @@
         <v>0.52</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J34" s="3">
         <v>0.24</v>
@@ -2625,7 +2629,7 @@
     </row>
     <row r="35" spans="1:17">
       <c r="A35" s="3">
-        <v>198</v>
+        <v>33</v>
       </c>
       <c r="B35" s="3">
         <v>90.1</v>
@@ -2649,7 +2653,7 @@
         <v>0.5</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J35" s="3">
         <v>0.26</v>
@@ -2680,7 +2684,7 @@
     </row>
     <row r="36" spans="1:17">
       <c r="A36" s="3">
-        <v>199</v>
+        <v>34</v>
       </c>
       <c r="B36" s="3">
         <v>89.5</v>
@@ -2704,7 +2708,7 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J36" s="3">
         <v>0.23</v>
@@ -2735,7 +2739,7 @@
     </row>
     <row r="37" spans="1:17">
       <c r="A37" s="3">
-        <v>200</v>
+        <v>35</v>
       </c>
       <c r="B37" s="3">
         <v>88.9</v>
@@ -2759,7 +2763,7 @@
         <v>0.45</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J37" s="3">
         <v>0.2</v>
@@ -2790,7 +2794,7 @@
     </row>
     <row r="38" spans="1:17">
       <c r="A38" s="3">
-        <v>201</v>
+        <v>36</v>
       </c>
       <c r="B38" s="3">
         <v>88.4</v>
@@ -2814,7 +2818,7 @@
         <v>0.33</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J38" s="3">
         <v>0.39</v>
@@ -2845,7 +2849,7 @@
     </row>
     <row r="39" spans="1:17">
       <c r="A39" s="3">
-        <v>202</v>
+        <v>37</v>
       </c>
       <c r="B39" s="3">
         <v>86.6</v>
@@ -2869,7 +2873,7 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J39" s="3">
         <v>0.38</v>
@@ -2900,7 +2904,7 @@
     </row>
     <row r="40" spans="1:17">
       <c r="A40" s="3">
-        <v>203</v>
+        <v>38</v>
       </c>
       <c r="B40" s="3">
         <v>85.7</v>
@@ -2924,7 +2928,7 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J40" s="3">
         <v>0.33</v>
@@ -2955,7 +2959,7 @@
     </row>
     <row r="41" spans="1:17">
       <c r="A41" s="3">
-        <v>204</v>
+        <v>39</v>
       </c>
       <c r="B41" s="3">
         <v>84.8</v>
@@ -2979,7 +2983,7 @@
         <v>0.54</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J41" s="3">
         <v>0.39</v>
@@ -3010,7 +3014,7 @@
     </row>
     <row r="42" spans="1:17">
       <c r="A42" s="3">
-        <v>205</v>
+        <v>40</v>
       </c>
       <c r="B42" s="3">
         <v>84.7</v>
@@ -3034,7 +3038,7 @@
         <v>0.54</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J42" s="3">
         <v>0.41</v>
@@ -3065,7 +3069,7 @@
     </row>
     <row r="43" spans="1:17">
       <c r="A43" s="3">
-        <v>206</v>
+        <v>41</v>
       </c>
       <c r="B43" s="3">
         <v>84.8</v>
@@ -3089,7 +3093,7 @@
         <v>0.54</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J43" s="3">
         <v>0.33</v>
@@ -3120,7 +3124,7 @@
     </row>
     <row r="44" spans="1:17">
       <c r="A44" s="3">
-        <v>207</v>
+        <v>42</v>
       </c>
       <c r="B44" s="3">
         <v>84.6</v>
@@ -3144,7 +3148,7 @@
         <v>0.59</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J44" s="3">
         <v>0.28999999999999998</v>
@@ -3175,7 +3179,7 @@
     </row>
     <row r="45" spans="1:17">
       <c r="A45" s="3">
-        <v>208</v>
+        <v>43</v>
       </c>
       <c r="B45" s="3">
         <v>84.5</v>
@@ -3199,7 +3203,7 @@
         <v>0.64</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J45" s="3">
         <v>0.28000000000000003</v>
@@ -3230,7 +3234,7 @@
     </row>
     <row r="46" spans="1:17">
       <c r="A46" s="3">
-        <v>209</v>
+        <v>44</v>
       </c>
       <c r="B46" s="3">
         <v>84.6</v>
@@ -3254,7 +3258,7 @@
         <v>0.66</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J46" s="3">
         <v>0.26</v>
@@ -3285,7 +3289,7 @@
     </row>
     <row r="47" spans="1:17">
       <c r="A47" s="3">
-        <v>210</v>
+        <v>45</v>
       </c>
       <c r="B47" s="3">
         <v>84.2</v>
@@ -3309,7 +3313,7 @@
         <v>0.64</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J47" s="3">
         <v>0.31</v>
@@ -3340,7 +3344,7 @@
     </row>
     <row r="48" spans="1:17">
       <c r="A48" s="3">
-        <v>211</v>
+        <v>46</v>
       </c>
       <c r="B48" s="3">
         <v>83.1</v>
@@ -3364,7 +3368,7 @@
         <v>0.59</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J48" s="3">
         <v>0.25</v>
@@ -3395,7 +3399,7 @@
     </row>
     <row r="49" spans="1:17">
       <c r="A49" s="3">
-        <v>212</v>
+        <v>47</v>
       </c>
       <c r="B49" s="3">
         <v>82.1</v>
@@ -3419,7 +3423,7 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J49" s="3">
         <v>0.28999999999999998</v>
@@ -3450,7 +3454,7 @@
     </row>
     <row r="50" spans="1:17">
       <c r="A50" s="3">
-        <v>213</v>
+        <v>48</v>
       </c>
       <c r="B50" s="3">
         <v>81.5</v>
@@ -3474,7 +3478,7 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J50" s="3">
         <v>0.31</v>
@@ -3505,7 +3509,7 @@
     </row>
     <row r="51" spans="1:17">
       <c r="A51" s="3">
-        <v>214</v>
+        <v>49</v>
       </c>
       <c r="B51" s="3">
         <v>80.599999999999994</v>
@@ -3529,7 +3533,7 @@
         <v>0.5</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J51" s="3">
         <v>0.38</v>
@@ -3560,7 +3564,7 @@
     </row>
     <row r="52" spans="1:17">
       <c r="A52" s="3">
-        <v>215</v>
+        <v>50</v>
       </c>
       <c r="B52" s="3">
         <v>79.7</v>
@@ -3584,7 +3588,7 @@
         <v>0.48</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J52" s="3">
         <v>0.51</v>
@@ -3615,7 +3619,7 @@
     </row>
     <row r="53" spans="1:17">
       <c r="A53" s="3">
-        <v>216</v>
+        <v>51</v>
       </c>
       <c r="B53" s="3">
         <v>79.8</v>
@@ -3639,7 +3643,7 @@
         <v>0.72</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J53" s="3">
         <v>0.5</v>
@@ -3670,7 +3674,7 @@
     </row>
     <row r="54" spans="1:17">
       <c r="A54" s="3">
-        <v>217</v>
+        <v>52</v>
       </c>
       <c r="B54" s="3">
         <v>80</v>
@@ -3694,7 +3698,7 @@
         <v>0.71</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J54" s="3">
         <v>0.35</v>
@@ -3725,7 +3729,7 @@
     </row>
     <row r="55" spans="1:17">
       <c r="A55" s="3">
-        <v>218</v>
+        <v>53</v>
       </c>
       <c r="B55" s="3">
         <v>79.400000000000006</v>
@@ -3749,7 +3753,7 @@
         <v>0.73</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J55" s="3">
         <v>0.48</v>
@@ -3780,7 +3784,7 @@
     </row>
     <row r="56" spans="1:17">
       <c r="A56" s="3">
-        <v>219</v>
+        <v>54</v>
       </c>
       <c r="B56" s="3">
         <v>78.5</v>
@@ -3804,7 +3808,7 @@
         <v>0.67</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J56" s="3">
         <v>0.37</v>
@@ -3835,7 +3839,7 @@
     </row>
     <row r="57" spans="1:17">
       <c r="A57" s="3">
-        <v>220</v>
+        <v>55</v>
       </c>
       <c r="B57" s="3">
         <v>78</v>
@@ -3859,7 +3863,7 @@
         <v>0.57999999999999996</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J57" s="3">
         <v>0.38</v>
@@ -3890,7 +3894,7 @@
     </row>
     <row r="58" spans="1:17">
       <c r="A58" s="3">
-        <v>221</v>
+        <v>56</v>
       </c>
       <c r="B58" s="3">
         <v>78.3</v>
@@ -3914,7 +3918,7 @@
         <v>0.54</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J58" s="3">
         <v>0.44</v>
@@ -3945,7 +3949,7 @@
     </row>
     <row r="59" spans="1:17">
       <c r="A59" s="3">
-        <v>222</v>
+        <v>57</v>
       </c>
       <c r="B59" s="3">
         <v>79.3</v>
@@ -3969,7 +3973,7 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J59" s="3">
         <v>0.53</v>
@@ -4000,7 +4004,7 @@
     </row>
     <row r="60" spans="1:17">
       <c r="A60" s="3">
-        <v>223</v>
+        <v>58</v>
       </c>
       <c r="B60" s="3">
         <v>80.2</v>
@@ -4024,7 +4028,7 @@
         <v>0.78</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J60" s="3">
         <v>0.42</v>
@@ -4055,7 +4059,7 @@
     </row>
     <row r="61" spans="1:17">
       <c r="A61" s="3">
-        <v>224</v>
+        <v>59</v>
       </c>
       <c r="B61" s="3">
         <v>80.8</v>
@@ -4079,7 +4083,7 @@
         <v>0.8</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J61" s="3">
         <v>0.4</v>
@@ -4129,7 +4133,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18.649999999999999" customHeight="1">
       <c r="A1" s="17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -4137,40 +4141,40 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="C3" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="D3" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="F3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B4" s="13">
         <f>COUNT(Data!G2:G61)</f>
         <v>60</v>
       </c>
       <c r="C4" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="F4" t="s">
         <v>26</v>
-      </c>
-      <c r="F4" t="s">
-        <v>27</v>
       </c>
       <c r="G4">
         <f>B5</f>
@@ -4179,20 +4183,20 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B5" s="13">
         <f>AVERAGE(Data!Q2:Q61)</f>
         <v>1.1433333333333335</v>
       </c>
       <c r="C5" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="F5" t="s">
         <v>29</v>
-      </c>
-      <c r="F5" t="s">
-        <v>30</v>
       </c>
       <c r="G5">
         <f>B6</f>
@@ -4201,20 +4205,20 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B6" s="13">
         <f>SQRT(SUMSQ(Data!P2:P61)/COUNT(Data!P2:P61))</f>
         <v>1.5531688038759122</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D6" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" t="s">
         <v>31</v>
-      </c>
-      <c r="F6" t="s">
-        <v>32</v>
       </c>
       <c r="G6">
         <f>B7</f>
@@ -4223,102 +4227,102 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B7" s="13">
         <f>MAX(Data!Q2:Q61)</f>
         <v>5.2000000000000028</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B8" s="13">
         <f>STDEV(Data!G2:G61)</f>
         <v>3.538345235509067</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B9" s="15">
         <f>COUNTIF(Data!I2:I61,"HOLD")/COUNTA(Data!I2:I61)</f>
         <v>0</v>
       </c>
       <c r="C9" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="11" t="s">
         <v>37</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B10" s="13">
         <f>AVERAGE(Data!H2:H61)</f>
         <v>0.57433333333333336</v>
       </c>
       <c r="C10" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" s="11" t="s">
         <v>40</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B11" s="13">
         <f>AVERAGE(Data!O2:O61)</f>
         <v>83.95</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B12" s="14">
         <f>AVERAGE(Data!G2:G61)</f>
         <v>83.333333333333329</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="16" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="19" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B16" s="19"/>
       <c r="C16" s="19"/>
@@ -4326,7 +4330,7 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="19" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B17" s="19"/>
       <c r="C17" s="19"/>
